--- a/docs/CodeSystem-diving-medicine-cs.xlsx
+++ b/docs/CodeSystem-diving-medicine-cs.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.5.6</t>
+    <t>0.5.8</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-12-30T19:11:20-07:00</t>
+    <t>2026-02-02T11:11:20-06:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/CodeSystem-diving-medicine-cs.xlsx
+++ b/docs/CodeSystem-diving-medicine-cs.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.5.8</t>
+    <t>0.5.9</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-02-02T11:11:20-06:00</t>
+    <t>2026-02-04T10:26:00-06:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/CodeSystem-diving-medicine-cs.xlsx
+++ b/docs/CodeSystem-diving-medicine-cs.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.5.12</t>
+    <t>0.6.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-25T00:24:16-05:00</t>
+    <t>2026-05-25T15:07:02-06:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/CodeSystem-diving-medicine-cs.xlsx
+++ b/docs/CodeSystem-diving-medicine-cs.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.6.0</t>
+    <t>0.6.2</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-25T15:07:02-06:00</t>
+    <t>2026-08-03T22:31:50-05:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/CodeSystem-diving-medicine-cs.xlsx
+++ b/docs/CodeSystem-diving-medicine-cs.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="165" uniqueCount="135">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="186" uniqueCount="150">
   <si>
     <t>Property</t>
   </si>
@@ -24,13 +24,13 @@
     <t>URL</t>
   </si>
   <si>
-    <t>https://mitre.org/fhir/space-health/CodeSystem/diving-medicine-cs</t>
+    <t>https://awatson1978.github.io/aerospace-medicine-ig/CodeSystem/diving-medicine-cs</t>
   </si>
   <si>
     <t>Version</t>
   </si>
   <si>
-    <t>0.6.2</t>
+    <t>0.7.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -54,13 +54,13 @@
     <t>Experimental</t>
   </si>
   <si>
-    <t>false</t>
+    <t>true</t>
   </si>
   <si>
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-03T22:31:50-05:00</t>
+    <t>2026-09-02T13:24:45-05:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -93,12 +93,12 @@
     <t>Copyright</t>
   </si>
   <si>
+    <t>Copyright 2022-2026 The MITRE Corporation and Abigail Watson. Licensed under Creative Commons Attribution-NoDerivatives 4.0 International (CC BY-ND 4.0). Approved for Public Release; Distribution Unlimited. Public Release Case Number 25-1124.</t>
+  </si>
+  <si>
     <t>Case Sensitive</t>
   </si>
   <si>
-    <t>true</t>
-  </si>
-  <si>
     <t>Value Set (all codes)</t>
   </si>
   <si>
@@ -123,7 +123,7 @@
     <t>Count</t>
   </si>
   <si>
-    <t>31</t>
+    <t>36</t>
   </si>
   <si>
     <t>Level</t>
@@ -418,6 +418,51 @@
   </si>
   <si>
     <t>Response to life support equipment failure</t>
+  </si>
+  <si>
+    <t>emergency-procedures</t>
+  </si>
+  <si>
+    <t>Emergency Procedures Invoked</t>
+  </si>
+  <si>
+    <t>Emergency procedures invoked during a dive, recorded as part of the dive profile</t>
+  </si>
+  <si>
+    <t>ear-barotrauma</t>
+  </si>
+  <si>
+    <t>Ear Barotrauma</t>
+  </si>
+  <si>
+    <t>Pressure injury to the middle or inner ear</t>
+  </si>
+  <si>
+    <t>pulmonary-barotrauma</t>
+  </si>
+  <si>
+    <t>Pulmonary Barotrauma</t>
+  </si>
+  <si>
+    <t>Pressure injury to the lungs from expanding gas during ascent</t>
+  </si>
+  <si>
+    <t>sinus-barotrauma</t>
+  </si>
+  <si>
+    <t>Sinus Barotrauma</t>
+  </si>
+  <si>
+    <t>Pressure injury to the paranasal sinuses</t>
+  </si>
+  <si>
+    <t>dental-barotrauma</t>
+  </si>
+  <si>
+    <t>Dental Barotrauma</t>
+  </si>
+  <si>
+    <t>Pressure-related dental pain or injury (barodontalgia)</t>
   </si>
 </sst>
 </file>
@@ -664,14 +709,16 @@
       <c r="A14" t="s" s="2">
         <v>25</v>
       </c>
-      <c r="B14" s="2"/>
+      <c r="B14" t="s" s="2">
+        <v>26</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="s" s="2">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="B15" t="s" s="2">
-        <v>27</v>
+        <v>13</v>
       </c>
     </row>
     <row r="16">
@@ -727,7 +774,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:D32"/>
+  <dimension ref="A1:D37"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <sheetData>
     <row r="1">
@@ -1178,6 +1225,76 @@
         <v>134</v>
       </c>
     </row>
+    <row r="33">
+      <c r="A33" t="s" s="2">
+        <v>41</v>
+      </c>
+      <c r="B33" t="s" s="2">
+        <v>135</v>
+      </c>
+      <c r="C33" t="s" s="2">
+        <v>136</v>
+      </c>
+      <c r="D33" t="s" s="2">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="s" s="2">
+        <v>41</v>
+      </c>
+      <c r="B34" t="s" s="2">
+        <v>138</v>
+      </c>
+      <c r="C34" t="s" s="2">
+        <v>139</v>
+      </c>
+      <c r="D34" t="s" s="2">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="s" s="2">
+        <v>41</v>
+      </c>
+      <c r="B35" t="s" s="2">
+        <v>141</v>
+      </c>
+      <c r="C35" t="s" s="2">
+        <v>142</v>
+      </c>
+      <c r="D35" t="s" s="2">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="s" s="2">
+        <v>41</v>
+      </c>
+      <c r="B36" t="s" s="2">
+        <v>144</v>
+      </c>
+      <c r="C36" t="s" s="2">
+        <v>145</v>
+      </c>
+      <c r="D36" t="s" s="2">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="s" s="2">
+        <v>41</v>
+      </c>
+      <c r="B37" t="s" s="2">
+        <v>147</v>
+      </c>
+      <c r="C37" t="s" s="2">
+        <v>148</v>
+      </c>
+      <c r="D37" t="s" s="2">
+        <v>149</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
 </worksheet>
